--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\540 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2490C559-BDB0-4B3D-9DEE-80DC15E4A6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7F1D36-E199-4FB5-81FB-C32725A7EDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -91,6 +91,33 @@
   </si>
   <si>
     <t>PICA DE PUESTA A TIERRA 100µ - Ø 14,2 LONG 1,5 METROS</t>
+  </si>
+  <si>
+    <t>Cable Topsolar PV H1Z272-K 1x6 1500 V -Negro (1 metro)</t>
+  </si>
+  <si>
+    <t>CABLE TOPSOLAR PV H1Z272-K 1X6 1500 V -ROJO (1 metro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONECTOR C43                  </t>
+  </si>
+  <si>
+    <t>KIT FIJACIÓN GRAPA C43 A PREMONTADO C43</t>
+  </si>
+  <si>
+    <t>PANEL SOLAR BIFACIAL 595W TRINA SOLAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERFIL C43 A 1800 Aluminio Bruto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERFIL C43 A 2400 Aluminio Bruto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPA PLÁSTICO PERFIL C43 </t>
+  </si>
+  <si>
+    <t>TORNILLO PARA CONECTOR 4,2 19ZN</t>
   </si>
 </sst>
 </file>
@@ -468,31 +495,31 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1">
-        <v>2160</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1">
-        <v>1620</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>32400</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>1620</v>
@@ -500,31 +527,31 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1">
-        <v>2160</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1">
-        <v>2700</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>2700</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1">
         <v>2160</v>
@@ -532,73 +559,145 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>2160</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>8640</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>1080</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>75060</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>12960</v>
+        <v>8640</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>8100</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1">
-        <v>10800</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1">
-        <v>48060</v>
+        <v>102060</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1">
+        <v>75060</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="1">
+        <v>12960</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="1">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1">
+        <v>24300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="1">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="1">
+        <v>48060</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B30" s="1">
         <v>29700</v>
       </c>
     </row>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\540 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7F1D36-E199-4FB5-81FB-C32725A7EDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AAE16B-2E21-445E-9A44-9EB8C4F784B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,7 +618,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="1">
-        <v>102060</v>
+        <v>96660</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\540 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\550 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AAE16B-2E21-445E-9A44-9EB8C4F784B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283BD579-3E16-4EE3-8374-985DB8FC2FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3240</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -498,7 +498,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="1">
-        <v>1890</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -506,7 +506,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="1">
-        <v>1890</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>2160</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -522,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -530,7 +530,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -538,7 +538,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="1">
-        <v>32400</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>1620</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>2160</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -570,7 +570,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>2700</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>2160</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>2160</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>8640</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -602,7 +602,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1890</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -610,7 +610,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -618,7 +618,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="1">
-        <v>96660</v>
+        <v>98450</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -626,7 +626,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="1">
-        <v>75060</v>
+        <v>76450</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -634,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="1">
-        <v>12960</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -642,7 +642,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="1">
-        <v>18900</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -650,7 +650,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="1">
-        <v>24300</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -658,7 +658,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="1">
-        <v>8100</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -666,7 +666,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="1">
-        <v>10800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -674,7 +674,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="1">
-        <v>48060</v>
+        <v>48950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -682,7 +682,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="1">
-        <v>1080</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -690,7 +690,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -698,7 +698,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="1">
-        <v>29700</v>
+        <v>30250</v>
       </c>
     </row>
     <row r="35" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\550 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\560 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283BD579-3E16-4EE3-8374-985DB8FC2FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206E6A6E-5378-4E47-BE88-1365ED10C4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3300</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -498,7 +498,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="1">
-        <v>1925</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -506,7 +506,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="1">
-        <v>1925</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -522,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -530,7 +530,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -538,7 +538,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="1">
-        <v>33000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -570,7 +570,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>2750</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>2200</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1">
-        <v>8800</v>
+        <v>8960</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -602,7 +602,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1925</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -610,7 +610,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -618,7 +618,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="1">
-        <v>98450</v>
+        <v>100240</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -626,7 +626,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="1">
-        <v>76450</v>
+        <v>77840</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -634,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="1">
-        <v>13200</v>
+        <v>13440</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -642,7 +642,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="1">
-        <v>19250</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -650,7 +650,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -658,7 +658,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="1">
-        <v>8250</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -666,7 +666,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="1">
-        <v>11000</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -674,7 +674,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="1">
-        <v>48950</v>
+        <v>49840</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -682,7 +682,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="1">
-        <v>1100</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -690,7 +690,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -698,7 +698,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="1">
-        <v>30250</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="35" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\560 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\570 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206E6A6E-5378-4E47-BE88-1365ED10C4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAC4868-CFF6-42B8-BDAF-26D85C9AAA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -72,9 +72,6 @@
     <t>LLAVE PARA INSTALACIÓN MC4</t>
   </si>
   <si>
-    <t>PANEL SOLAR MONOFACIAL 505W TRINA SOLAR</t>
-  </si>
-  <si>
     <t>PERFIL C43 A 1200 ANONIZADO</t>
   </si>
   <si>
@@ -118,6 +115,27 @@
   </si>
   <si>
     <t>TORNILLO PARA CONECTOR 4,2 19ZN</t>
+  </si>
+  <si>
+    <t>ANCLAJE PARA TEJA M10X250 A2 (SIN TACO)</t>
+  </si>
+  <si>
+    <t>CABLE TOXFREE H07Z1-K TYPE 2 (AS) 1 X 6 MM² CPR NEGRO (1 METRO)</t>
+  </si>
+  <si>
+    <t>KIT FIJACIÓN C43 A CHAPA GRECADA CON JUNTA EPDM</t>
+  </si>
+  <si>
+    <t>MICROPERFIL C34 A 150 BR. (SUSTITUYE AL C36)</t>
+  </si>
+  <si>
+    <t>PANEL SOLAR BIFACIAL 505W TRINA SOLAR</t>
+  </si>
+  <si>
+    <t>TORNILLO AUTOTALADRANTE 5,5X25 + ARANDELA E16 CON EPDM</t>
+  </si>
+  <si>
+    <t>TUBO CORRUGADO NEGRO 32MMX50MTRS (1 METRO)</t>
   </si>
 </sst>
 </file>
@@ -474,235 +492,280 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3360</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>1680</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1680</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1960</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1">
-        <v>1960</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
-        <v>2240</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>1680</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1120</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>33600</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1">
-        <v>1680</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>2240</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>2800</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>2800</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>2240</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>2240</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>8960</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>1960</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>1120</v>
+        <v>9120</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1">
-        <v>100240</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>77840</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1">
-        <v>13440</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1">
-        <v>19600</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1">
-        <v>25200</v>
+        <v>96330</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>8400</v>
+        <v>102030</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>11200</v>
+        <v>13680</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>49840</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>1120</v>
+        <v>25650</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B29" s="1">
-        <v>112</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1">
-        <v>30800</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="4"/>
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="1">
+        <v>50730</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="1">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="1">
+        <v>31350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1425</v>
+      </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="4"/>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\570 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\580 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAC4868-CFF6-42B8-BDAF-26D85C9AAA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E024BFD4-E639-4EB0-B657-105A0FB8E1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3420</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -500,7 +500,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -516,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -524,7 +524,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="1">
-        <v>1995</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -532,7 +532,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="1">
-        <v>1995</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -548,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -556,7 +556,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>1995</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -564,7 +564,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -572,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>34200</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>1710</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -588,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -612,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>2280</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -628,7 +628,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>9120</v>
+        <v>9280</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -636,7 +636,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="1">
-        <v>2850</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -644,7 +644,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>1995</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -652,7 +652,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -660,7 +660,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="1">
-        <v>4560</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -668,7 +668,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1">
-        <v>96330</v>
+        <v>98020</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -676,7 +676,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>102030</v>
+        <v>103820</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>13680</v>
+        <v>13920</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -692,7 +692,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>19950</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -700,7 +700,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>25650</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -708,7 +708,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="1">
-        <v>8550</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -716,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="1">
-        <v>11400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -724,7 +724,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="1">
-        <v>50730</v>
+        <v>51620</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -732,7 +732,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>1140</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -740,7 +740,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1">
-        <v>855</v>
+        <v>870</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -748,7 +748,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -756,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="1">
-        <v>31350</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -764,7 +764,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>1425</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="54" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\580 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\590 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E024BFD4-E639-4EB0-B657-105A0FB8E1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC0EA51-A99A-4759-86EE-6AB5C28FECB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3480</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -500,7 +500,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -516,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -524,7 +524,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="1">
-        <v>2030</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -532,7 +532,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="1">
-        <v>2030</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -548,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -556,7 +556,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>2030</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -564,7 +564,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -572,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>34800</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>1740</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -588,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -612,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>2320</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -628,7 +628,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>9280</v>
+        <v>9440</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -636,7 +636,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="1">
-        <v>2900</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -644,7 +644,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>2030</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -652,7 +652,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -660,7 +660,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="1">
-        <v>4640</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -668,7 +668,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1">
-        <v>98020</v>
+        <v>99710</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -676,7 +676,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>103820</v>
+        <v>105610</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>13920</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -692,7 +692,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>20300</v>
+        <v>20650</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -700,7 +700,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>26100</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -708,7 +708,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="1">
-        <v>8700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -716,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="1">
-        <v>11600</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -724,7 +724,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="1">
-        <v>51620</v>
+        <v>52510</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -732,7 +732,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>1160</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -740,7 +740,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1">
-        <v>870</v>
+        <v>885</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -748,7 +748,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -756,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="1">
-        <v>31900</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -764,7 +764,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>1450</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="54" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\590 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\600 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC0EA51-A99A-4759-86EE-6AB5C28FECB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A6DA72-1763-49C3-8E43-22D3A5688EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3540</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -500,7 +500,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -516,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -524,7 +524,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="1">
-        <v>2065</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -532,7 +532,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="1">
-        <v>2065</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -548,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -556,7 +556,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>2065</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -564,7 +564,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -572,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>35400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>1770</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -588,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -612,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>2360</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -628,7 +628,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>9440</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -636,7 +636,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="1">
-        <v>2950</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -644,7 +644,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>2065</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -652,7 +652,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -660,7 +660,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="1">
-        <v>4720</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -668,7 +668,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1">
-        <v>99710</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -676,7 +676,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>105610</v>
+        <v>107400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>14160</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -692,7 +692,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>20650</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -700,7 +700,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>26550</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -708,7 +708,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="1">
-        <v>8850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -716,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="1">
-        <v>11800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -724,7 +724,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="1">
-        <v>52510</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -732,7 +732,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>1180</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -740,7 +740,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1">
-        <v>885</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -748,7 +748,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -756,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="1">
-        <v>32450</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -764,7 +764,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>1475</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="54" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\600 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\610 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A6DA72-1763-49C3-8E43-22D3A5688EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ED938C-5732-4104-952B-9A83A1F6C03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>PICA DE PUESTA A TIERRA 100µ - Ø 14,2 LONG 1,5 METROS</t>
   </si>
   <si>
-    <t>Cable Topsolar PV H1Z272-K 1x6 1500 V -Negro (1 metro)</t>
-  </si>
-  <si>
     <t>CABLE TOPSOLAR PV H1Z272-K 1X6 1500 V -ROJO (1 metro)</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>TUBO CORRUGADO NEGRO 32MMX50MTRS (1 METRO)</t>
+  </si>
+  <si>
+    <t>CABLE TOPSOLAR PV H1Z272-K 1x6 1500 V -Negro (1 metro)</t>
   </si>
 </sst>
 </file>
@@ -492,15 +492,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3600</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -516,23 +516,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1">
-        <v>2100</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
-        <v>2100</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -548,23 +548,23 @@
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
-        <v>2100</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -572,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>36000</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>1800</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -588,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -612,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>2400</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -628,23 +628,23 @@
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>9600</v>
+        <v>9760</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>2100</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -652,31 +652,31 @@
         <v>14</v>
       </c>
       <c r="B22" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1">
-        <v>4800</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1">
-        <v>101400</v>
+        <v>103090</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>107400</v>
+        <v>109190</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -684,23 +684,23 @@
         <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>14400</v>
+        <v>14640</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1">
-        <v>21000</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1">
-        <v>27000</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -708,7 +708,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="1">
-        <v>9000</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -716,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="1">
-        <v>12000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -724,31 +724,31 @@
         <v>17</v>
       </c>
       <c r="B31" s="1">
-        <v>53400</v>
+        <v>54290</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -756,15 +756,15 @@
         <v>18</v>
       </c>
       <c r="B35" s="1">
-        <v>33000</v>
+        <v>33550</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>1500</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="54" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\610 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\620 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ED938C-5732-4104-952B-9A83A1F6C03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E9B9E6-EC36-4E94-AF4A-F943134C0990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3660</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -500,7 +500,7 @@
         <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -508,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -516,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -524,7 +524,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="1">
-        <v>2135</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -532,7 +532,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="1">
-        <v>2135</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -548,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -556,7 +556,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="1">
-        <v>2135</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -564,7 +564,7 @@
         <v>22</v>
       </c>
       <c r="B11" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -572,7 +572,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>36600</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -580,7 +580,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>1830</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -588,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -612,7 +612,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>2440</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -628,7 +628,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>9760</v>
+        <v>9920</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -636,7 +636,7 @@
         <v>31</v>
       </c>
       <c r="B20" s="1">
-        <v>3050</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -644,7 +644,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>2135</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -652,7 +652,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -660,7 +660,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="1">
-        <v>4880</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -668,7 +668,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="1">
-        <v>103090</v>
+        <v>104780</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -676,7 +676,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>109190</v>
+        <v>110980</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>14640</v>
+        <v>14880</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -692,7 +692,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="1">
-        <v>21350</v>
+        <v>21700</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -700,7 +700,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="1">
-        <v>27450</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -708,7 +708,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="1">
-        <v>9150</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -716,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="1">
-        <v>12200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -724,7 +724,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="1">
-        <v>54290</v>
+        <v>55180</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -732,7 +732,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1">
-        <v>1220</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -740,7 +740,7 @@
         <v>34</v>
       </c>
       <c r="B33" s="1">
-        <v>915</v>
+        <v>930</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -748,7 +748,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -756,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="B35" s="1">
-        <v>33550</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -764,7 +764,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>1525</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="54" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\620 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\640 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E9B9E6-EC36-4E94-AF4A-F943134C0990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D210F9CD-3E9B-4067-BBF6-21B42D6DC9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>DESCRIPCION</t>
   </si>
   <si>
-    <t>PRECIO CUP</t>
-  </si>
-  <si>
     <t>ANCLAJE PARA HORMIGÓN M12X140 + TORNILLERÍA</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
     <t>KIT FIJACIÓN GRAPA C43 A PREMONTADO C43</t>
   </si>
   <si>
-    <t>PANEL SOLAR BIFACIAL 595W TRINA SOLAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">PERFIL C43 A 1800 Aluminio Bruto </t>
   </si>
   <si>
@@ -136,13 +130,19 @@
   </si>
   <si>
     <t>CABLE TOPSOLAR PV H1Z272-K 1x6 1500 V -Negro (1 metro)</t>
+  </si>
+  <si>
+    <t>PRECIO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -154,6 +154,10 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -185,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -197,6 +201,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,287 +489,279 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>3720</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="1">
-        <v>4960</v>
+        <v>27</v>
+      </c>
+      <c r="B3" s="5">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
         <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1860</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1860</v>
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2170</v>
+        <v>34</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2170</v>
+        <v>20</v>
+      </c>
+      <c r="B7" s="5">
+        <v>3.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2480</v>
+        <v>4</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1860</v>
+        <v>5</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2170</v>
+        <v>28</v>
+      </c>
+      <c r="B10" s="5">
+        <v>3.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1240</v>
+        <v>21</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1">
-        <v>37200</v>
+        <v>18</v>
+      </c>
+      <c r="B12" s="5">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1860</v>
+        <v>6</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2480</v>
+        <v>7</v>
+      </c>
+      <c r="B14" s="5">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="1">
-        <v>3100</v>
+        <v>8</v>
+      </c>
+      <c r="B15" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="1">
-        <v>3100</v>
+        <v>9</v>
+      </c>
+      <c r="B16" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2480</v>
+        <v>10</v>
+      </c>
+      <c r="B17" s="5">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2480</v>
+        <v>11</v>
+      </c>
+      <c r="B18" s="5">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1">
-        <v>9920</v>
+        <v>12</v>
+      </c>
+      <c r="B19" s="5">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="1">
-        <v>3100</v>
+        <v>29</v>
+      </c>
+      <c r="B20" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2170</v>
+        <v>22</v>
+      </c>
+      <c r="B21" s="5">
+        <v>3.5</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1240</v>
+        <v>13</v>
+      </c>
+      <c r="B22" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="1">
-        <v>4960</v>
+        <v>30</v>
+      </c>
+      <c r="B23" s="5">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1">
-        <v>104780</v>
+        <v>31</v>
+      </c>
+      <c r="B24" s="5">
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="5">
         <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <v>110980</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="1">
-        <v>14880</v>
+        <v>23</v>
+      </c>
+      <c r="B26" s="5">
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1">
-        <v>21700</v>
+        <v>24</v>
+      </c>
+      <c r="B27" s="5">
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1">
-        <v>27900</v>
+        <v>19</v>
+      </c>
+      <c r="B28" s="5">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5">
         <v>20</v>
-      </c>
-      <c r="B29" s="1">
-        <v>9300</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="1">
-        <v>12400</v>
+      <c r="B30" s="5">
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="1">
-        <v>55180</v>
+        <v>25</v>
+      </c>
+      <c r="B31" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1240</v>
+        <v>32</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1.5</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="1">
-        <v>930</v>
+        <v>26</v>
+      </c>
+      <c r="B33" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="1">
-        <v>124</v>
+      <c r="A34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="5">
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="1">
-        <v>34100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1">
-        <v>1550</v>
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5">
+        <v>2.5</v>
       </c>
     </row>
     <row r="54" spans="1:1">

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\640 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D210F9CD-3E9B-4067-BBF6-21B42D6DC9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198923C2-0D74-440C-B7DD-550513597DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,18 +69,12 @@
     <t>LLAVE PARA INSTALACIÓN MC4</t>
   </si>
   <si>
-    <t>PERFIL C43 A 1200 ANONIZADO</t>
-  </si>
-  <si>
     <t>PORTAFUSIBLE MC4 SCF/FUSE 1000V 20AMP</t>
   </si>
   <si>
     <t>PROTECTOR DE SOBRETENCIONES TRANSITORIAS DC TIPO 1 Y 2 UN 725  VDC / UC 1000 VDC</t>
   </si>
   <si>
-    <t>TRIÁNGULO ABIERTO C43 A 1625 15º</t>
-  </si>
-  <si>
     <t>CRIMPADORA PARA TERMINALES MC4</t>
   </si>
   <si>
@@ -133,6 +127,12 @@
   </si>
   <si>
     <t>PRECIO</t>
+  </si>
+  <si>
+    <t>PERFIL C43 A 1200 ANODIZADO</t>
+  </si>
+  <si>
+    <t>TRIÁNGULO ABIERTO C43 A 1625</t>
   </si>
 </sst>
 </file>
@@ -189,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -202,6 +202,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,11 +491,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
@@ -501,15 +503,15 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>27</v>
+      <c r="A3" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="B3" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="5">
@@ -517,7 +519,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5">
@@ -525,31 +527,31 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>34</v>
+      <c r="A6" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B6" s="5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>20</v>
+      <c r="A7" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="B7" s="5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="5">
@@ -557,39 +559,39 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>28</v>
+      <c r="A10" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="5">
         <v>3.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>21</v>
+      <c r="A11" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B11" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>18</v>
+      <c r="A12" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="B12" s="5">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="5">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="5">
@@ -597,7 +599,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="5">
@@ -605,7 +607,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="5">
@@ -613,7 +615,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B17" s="5">
@@ -621,7 +623,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="5">
@@ -629,7 +631,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="5">
@@ -638,22 +640,22 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>22</v>
+      <c r="A21" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="B21" s="5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="A22" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="5">
@@ -661,104 +663,104 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>30</v>
+      <c r="A23" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="B23" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>31</v>
+      <c r="A24" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="B24" s="5">
         <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>14</v>
+      <c r="A25" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B25" s="5">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>23</v>
+      <c r="A26" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B26" s="5">
         <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>24</v>
+      <c r="A27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B27" s="5">
         <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>19</v>
+      <c r="A28" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="B28" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="6" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>16</v>
       </c>
       <c r="B30" s="5">
         <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>25</v>
+      <c r="A31" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B31" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>32</v>
+      <c r="A32" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B32" s="5">
         <v>1.5</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>26</v>
+      <c r="A33" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="B33" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="4" t="s">
-        <v>17</v>
+      <c r="A34" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="B34" s="5">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>33</v>
+      <c r="A35" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B35" s="5">
         <v>2.5</v>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\640 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\680 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198923C2-0D74-440C-B7DD-550513597DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89184F8-4E3A-4C86-B973-B23C579F2A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -133,6 +133,18 @@
   </si>
   <si>
     <t>TRIÁNGULO ABIERTO C43 A 1625</t>
+  </si>
+  <si>
+    <t>ESTRUCTURA PARA 1 PANEL (CON TRIÁNGULOS ABIERTOS)</t>
+  </si>
+  <si>
+    <t>ESTRUCTURA PARA 2 PANELES (CON TRIÁNGULOS ABIERTOS)</t>
+  </si>
+  <si>
+    <t>ESTRUCTURA PARA 3 PANELES (CON TRIÁNGULOS ABIERTOS)</t>
+  </si>
+  <si>
+    <t>ESTRUCTURA PARA 4 PANELES (CON TRIÁNGULOS ABIERTOS)</t>
   </si>
 </sst>
 </file>
@@ -583,48 +595,48 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="6" t="s">
-        <v>6</v>
+      <c r="A13" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B13" s="5">
-        <v>3.5</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="6" t="s">
-        <v>7</v>
+      <c r="A14" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="B14" s="5">
-        <v>4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="6" t="s">
-        <v>8</v>
+      <c r="A15" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B15" s="5">
-        <v>5</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
+      <c r="A16" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B16" s="5">
-        <v>5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B17" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B18" s="5">
         <v>4</v>
@@ -632,23 +644,23 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B19" s="5">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>27</v>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="B20" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="7" t="s">
-        <v>20</v>
+      <c r="A21" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B21" s="5">
         <v>4</v>
@@ -656,113 +668,145 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B22" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="7" t="s">
-        <v>28</v>
+      <c r="A23" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="B23" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="7" t="s">
-        <v>29</v>
+      <c r="A24" t="s">
+        <v>27</v>
       </c>
       <c r="B24" s="5">
-        <v>169</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B25" s="5">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B26" s="5">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="6" t="s">
-        <v>22</v>
+      <c r="A27" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="B27" s="5">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B28" s="5">
-        <v>17</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="6" t="s">
-        <v>14</v>
+      <c r="A29" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B29" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B30" s="5">
-        <v>89</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" s="5">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B32" s="5">
-        <v>1.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B37" s="5">
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="7" t="s">
+    <row r="38" spans="1:2">
+      <c r="A38" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B38" s="5">
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="7" t="s">
+    <row r="39" spans="1:2">
+      <c r="A39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B39" s="5">
         <v>2.5</v>
       </c>
     </row>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\680 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\700 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89184F8-4E3A-4C86-B973-B23C579F2A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E2733C-4FE7-4834-9EDB-B0B86F868006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>ESTRUCTURA PARA 4 PANELES (CON TRIÁNGULOS ABIERTOS)</t>
+  </si>
+  <si>
+    <t>CONECTOR XT60I</t>
   </si>
 </sst>
 </file>
@@ -587,72 +590,72 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="5">
-        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5">
-        <v>452</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="5">
         <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="5">
-        <v>3.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" s="5">
         <v>5</v>
@@ -660,15 +663,15 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="5">
         <v>4</v>
@@ -676,137 +679,145 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B24" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B25" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="7" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B26" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="6" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B27" s="5">
         <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="5">
-        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="5">
-        <v>169</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B30" s="5">
         <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="5">
-        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B32" s="5">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="7" t="s">
+    <row r="33" spans="1:2">
+      <c r="A33" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B33" s="5">
         <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="5">
-        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" s="5">
-        <v>89</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B36" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="7" t="s">
+    <row r="37" spans="1:2">
+      <c r="A37" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B37" s="5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="6" t="s">
+    <row r="38" spans="1:2">
+      <c r="A38" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B38" s="5">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="5">
-        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B40" s="5">
         <v>2.5</v>
       </c>
     </row>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\700 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\685 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E2733C-4FE7-4834-9EDB-B0B86F868006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9483EA3-CC6C-45DB-AA06-6963FBCD9862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>CONECTOR XT60I</t>
+  </si>
+  <si>
+    <t>BRIDA</t>
+  </si>
+  <si>
+    <t>TACO BRIDA</t>
   </si>
 </sst>
 </file>
@@ -527,31 +533,31 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="B4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
-        <v>3</v>
       </c>
       <c r="B5" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="B7" s="5">
         <v>4</v>
@@ -559,111 +565,111 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5">
         <v>4</v>
-      </c>
-      <c r="B8" s="5">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="5">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="7" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B11" s="5">
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="6" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B12" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="6" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B14" s="5">
         <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="5">
-        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5">
-        <v>452</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B18" s="5">
         <v>500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="5">
-        <v>3.5</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="5">
         <v>5</v>
@@ -671,15 +677,15 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="5">
         <v>4</v>
@@ -687,137 +693,153 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B25" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B26" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="7" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B27" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="6" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B28" s="5">
         <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="5">
-        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5">
-        <v>169</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B31" s="5">
         <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="5">
-        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B33" s="5">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="7" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B34" s="5">
         <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="5">
-        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="5">
-        <v>89</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B36" s="5">
-        <v>2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="5">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B41" s="5">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="7" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B42" s="5">
         <v>2.5</v>
       </c>
     </row>

--- a/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
+++ b/energia-limpia/assets/downloads/TODITICO_CATÁLOGO_Energía_Limpia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\685 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\620 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9483EA3-CC6C-45DB-AA06-6963FBCD9862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17512648-3B96-4B6A-8E7B-DD4EF42D7EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -120,9 +120,6 @@
     <t>TORNILLO AUTOTALADRANTE 5,5X25 + ARANDELA E16 CON EPDM</t>
   </si>
   <si>
-    <t>TUBO CORRUGADO NEGRO 32MMX50MTRS (1 METRO)</t>
-  </si>
-  <si>
     <t>CABLE TOPSOLAR PV H1Z272-K 1x6 1500 V -Negro (1 metro)</t>
   </si>
   <si>
@@ -154,6 +151,18 @@
   </si>
   <si>
     <t>TACO BRIDA</t>
+  </si>
+  <si>
+    <t>CAJA DE DISTRIBUCIÓN PARA 8 POSICIONES IP40 CON PUERTA TRANSPARENTE</t>
+  </si>
+  <si>
+    <t>INTERRUPTOR TRANSFERENCIAL AUTOMÁTICO 3P/40A VOLTAJE DE L-N 110V</t>
+  </si>
+  <si>
+    <t>SECCIONADORES PORTAFUSIBLES 1P PARA FUSIBLE DE 10X38MM. TENSIÓN UE: 1000VCC</t>
+  </si>
+  <si>
+    <t>TUBO CORRUGADO NEGRO 32MM (1 METRO)</t>
   </si>
 </sst>
 </file>
@@ -512,7 +521,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -533,7 +542,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="5">
         <v>0.04</v>
@@ -557,7 +566,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5">
         <v>4</v>
@@ -596,88 +605,88 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="5">
+    <row r="14" spans="1:2">
+      <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="6" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B15" s="5">
         <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="5">
-        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="5">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" s="5">
-        <v>452</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5">
         <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="5">
-        <v>3.5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="5">
         <v>5</v>
@@ -685,162 +694,186 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B27" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B28" s="5">
         <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="5">
-        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B29" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="7" t="s">
-        <v>29</v>
+      <c r="A30" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="B30" s="5">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B31" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="6" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B34" s="5">
         <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="5">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="5">
-        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B37" s="5">
         <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="5">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5">
-        <v>0.1</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B38" s="5">
-        <v>2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5">
-        <v>1.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="6" t="s">
-        <v>24</v>
+      <c r="A40" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="B40" s="5">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="7" t="s">
-        <v>35</v>
+      <c r="A41" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B41" s="5">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42" s="5">
-        <v>2.5</v>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:1">
